--- a/artfynd/A 33003-2024 artfynd.xlsx
+++ b/artfynd/A 33003-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122979395</v>
       </c>
       <c r="B2" t="n">
-        <v>58187</v>
+        <v>58190</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 33003-2024 artfynd.xlsx
+++ b/artfynd/A 33003-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122979395</v>
       </c>
       <c r="B2" t="n">
-        <v>58190</v>
+        <v>58196</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 33003-2024 artfynd.xlsx
+++ b/artfynd/A 33003-2024 artfynd.xlsx
@@ -678,16 +678,11 @@
         <v>122979395</v>
       </c>
       <c r="B2" t="n">
-        <v>58196</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58649</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">

--- a/artfynd/A 33003-2024 artfynd.xlsx
+++ b/artfynd/A 33003-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AZ2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -796,8 +801,16 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122979395</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 33003-2024 artfynd.xlsx
+++ b/artfynd/A 33003-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ2"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -807,9 +807,333 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>135694370</v>
+      </c>
+      <c r="B3" t="n">
+        <v>110030</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>220228</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Sommarfibbla</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Leontodon hispidus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Värna, Ög</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>545898</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6445484</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Kinda</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Tjärstad</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Hugo Axelsson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Hugo Axelsson, Emma Nordenberg</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135694370</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>135694371</v>
+      </c>
+      <c r="B4" t="n">
+        <v>110242</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Dödvik, Ög</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>546024</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6445637</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Kinda</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Tjärstad</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Emma Nordenberg</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Emma Nordenberg, Hugo Axelsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135694371</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>135694392</v>
+      </c>
+      <c r="B5" t="n">
+        <v>110242</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Dödvik, Ög</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>545984</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6445646</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Kinda</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Tjärstad</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Emma Nordenberg</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Emma Nordenberg, Hugo Axelsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135694392</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 33003-2024 artfynd.xlsx
+++ b/artfynd/A 33003-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ2"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -807,9 +807,333 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>135694370</v>
+      </c>
+      <c r="B3" t="n">
+        <v>110035</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>220228</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Sommarfibbla</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Leontodon hispidus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Värna, Ög</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>545898</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6445484</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Kinda</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Tjärstad</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Hugo Axelsson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Hugo Axelsson, Emma Nordenberg</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135694370</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>135694371</v>
+      </c>
+      <c r="B4" t="n">
+        <v>110247</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Dödvik, Ög</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>546024</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6445637</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Kinda</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Tjärstad</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Emma Nordenberg</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Emma Nordenberg, Hugo Axelsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135694371</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>135694392</v>
+      </c>
+      <c r="B5" t="n">
+        <v>110247</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Dödvik, Ög</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>545984</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6445646</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Kinda</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Tjärstad</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Emma Nordenberg</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Emma Nordenberg, Hugo Axelsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135694392</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 33003-2024 artfynd.xlsx
+++ b/artfynd/A 33003-2024 artfynd.xlsx
@@ -812,7 +812,7 @@
         <v>135694370</v>
       </c>
       <c r="B3" t="n">
-        <v>110035</v>
+        <v>110037</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -919,7 +919,7 @@
         <v>135694371</v>
       </c>
       <c r="B4" t="n">
-        <v>110247</v>
+        <v>110249</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>135694392</v>
       </c>
       <c r="B5" t="n">
-        <v>110247</v>
+        <v>110249</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 33003-2024 artfynd.xlsx
+++ b/artfynd/A 33003-2024 artfynd.xlsx
@@ -812,7 +812,7 @@
         <v>135694370</v>
       </c>
       <c r="B3" t="n">
-        <v>110037</v>
+        <v>110060</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -919,7 +919,7 @@
         <v>135694371</v>
       </c>
       <c r="B4" t="n">
-        <v>110249</v>
+        <v>110272</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>135694392</v>
       </c>
       <c r="B5" t="n">
-        <v>110249</v>
+        <v>110272</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 33003-2024 artfynd.xlsx
+++ b/artfynd/A 33003-2024 artfynd.xlsx
@@ -812,7 +812,7 @@
         <v>135694370</v>
       </c>
       <c r="B3" t="n">
-        <v>110060</v>
+        <v>110062</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -919,7 +919,7 @@
         <v>135694371</v>
       </c>
       <c r="B4" t="n">
-        <v>110272</v>
+        <v>110274</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>135694392</v>
       </c>
       <c r="B5" t="n">
-        <v>110272</v>
+        <v>110274</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 33003-2024 artfynd.xlsx
+++ b/artfynd/A 33003-2024 artfynd.xlsx
@@ -812,7 +812,7 @@
         <v>135694370</v>
       </c>
       <c r="B3" t="n">
-        <v>110062</v>
+        <v>110063</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -919,7 +919,7 @@
         <v>135694371</v>
       </c>
       <c r="B4" t="n">
-        <v>110274</v>
+        <v>110275</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>135694392</v>
       </c>
       <c r="B5" t="n">
-        <v>110274</v>
+        <v>110275</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 33003-2024 artfynd.xlsx
+++ b/artfynd/A 33003-2024 artfynd.xlsx
@@ -812,7 +812,7 @@
         <v>135694370</v>
       </c>
       <c r="B3" t="n">
-        <v>110063</v>
+        <v>110064</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -919,7 +919,7 @@
         <v>135694371</v>
       </c>
       <c r="B4" t="n">
-        <v>110275</v>
+        <v>110276</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>135694392</v>
       </c>
       <c r="B5" t="n">
-        <v>110275</v>
+        <v>110276</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 33003-2024 artfynd.xlsx
+++ b/artfynd/A 33003-2024 artfynd.xlsx
@@ -812,7 +812,7 @@
         <v>135694370</v>
       </c>
       <c r="B3" t="n">
-        <v>110064</v>
+        <v>110070</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -919,7 +919,7 @@
         <v>135694371</v>
       </c>
       <c r="B4" t="n">
-        <v>110276</v>
+        <v>110282</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>135694392</v>
       </c>
       <c r="B5" t="n">
-        <v>110276</v>
+        <v>110282</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 33003-2024 artfynd.xlsx
+++ b/artfynd/A 33003-2024 artfynd.xlsx
@@ -812,7 +812,7 @@
         <v>135694370</v>
       </c>
       <c r="B3" t="n">
-        <v>110070</v>
+        <v>110071</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -919,7 +919,7 @@
         <v>135694371</v>
       </c>
       <c r="B4" t="n">
-        <v>110282</v>
+        <v>110283</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>135694392</v>
       </c>
       <c r="B5" t="n">
-        <v>110282</v>
+        <v>110283</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 33003-2024 artfynd.xlsx
+++ b/artfynd/A 33003-2024 artfynd.xlsx
@@ -812,7 +812,7 @@
         <v>135694370</v>
       </c>
       <c r="B3" t="n">
-        <v>110071</v>
+        <v>110082</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -919,7 +919,7 @@
         <v>135694371</v>
       </c>
       <c r="B4" t="n">
-        <v>110283</v>
+        <v>110294</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>135694392</v>
       </c>
       <c r="B5" t="n">
-        <v>110283</v>
+        <v>110294</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
